--- a/forms/trg/Formulir_TRG_lolw.xlsx
+++ b/forms/trg/Formulir_TRG_lolw.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,33 +913,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Anie Asriany, M.Si</t>
+          <t>Prof. Dr. Ir. Muhammad Irfan Said, S.Pt, M.P, IPM, ASEAN Eng.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Livestock Waste and By-Product Processing Technology</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8824-4944</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6085895</t>
+          <t>6015290</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57205028122</t>
+          <t>56688183300</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Jamila Mustabi, S.Pt, M.Si, IPM</t>
+          <t>Dr. Ir. Anie Asriany, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -972,19 +976,15 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-1031-9889</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6017918</t>
+          <t>6085895</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>55792861500</t>
+          <t>57205028122</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -999,37 +999,37 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mehmet Mete Mutlu</t>
+          <t>Dr. Ir. Jamila Mustabi, S.Pt, M.Si, IPM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Ege university</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Leather Engineering</t>
-        </is>
-      </c>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2365-7887</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0002-1031-9889</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6017918</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57028602600</t>
+          <t>55792861500</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1044,22 +1044,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Maurizia Seggiani</t>
+          <t>Prof. Dr. Mehmet Mete Mutlu</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Pisa University, Italy</t>
+          <t>Ege university</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Leather Engineering</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,13 +1068,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9628-7178</t>
+          <t>0000-0002-2365-7887</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>6603755099</t>
+          <t>57028602600</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Konstantina Kollia</t>
+          <t>Prof. Dr. Maurizia Seggiani</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>National Technical University of Athens (NTUA)</t>
+          <t>Pisa University, Italy</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1113,13 +1113,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-9712-7685</t>
+          <t>0000-0002-9628-7178</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>6602223351</t>
+          <t>6603755099</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Hasan Ozgunay</t>
+          <t>Prof. Dr. Konstantina Kollia</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>University of EGE (Turkiye)</t>
+          <t>National Technical University of Athens (NTUA)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Leather Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1158,13 +1158,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7351-2603</t>
+          <t>0009-0005-9712-7685</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>8411629900</t>
+          <t>6602223351</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1179,37 +1179,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>La Ode Rahman Musawa, S.Pt, M.Si</t>
+          <t>Prof. Dr. Hasan Ozgunay</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
+          <t>University of EGE (Turkiye)</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Leather Engineering</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>my-orcid?orcid=0000-0003-3359-1698</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>6917485</t>
-        </is>
-      </c>
+          <t>0000-0001-7351-2603</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/home.uri?zone=header&amp;origin=sbrowse</t>
+          <t>8411629900</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Urfiana Sara</t>
+          <t>La Ode Rahman Musawa, S.Pt, M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1237,18 +1237,26 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Eco-Enzyme Technology and Applications</t>
-        </is>
-      </c>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>my-orcid?orcid=0000-0003-3359-1698</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>6917485</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/home.uri?zone=header&amp;origin=sbrowse</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1261,12 +1269,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Nur Fitri Ramadhan</t>
+          <t>Urfiana Sara</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1276,7 +1284,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Chemical, Enzymatic, and Microbial Hydrolysis Methods on the Characteristics of Horse Skin Gelatin and Its Application as a Wound Healing Therapeutic Agent</t>
+          <t>Eco-Enzyme Technology and Applications</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1298,12 +1306,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Haikal Kadir</t>
+          <t>Nur Fitri Ramadhan</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1313,7 +1321,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Fruits Waste Enzyme Technology</t>
+          <t>The Effect of Chemical, Enzymatic, and Microbial Hydrolysis Methods on the Characteristics of Horse Skin Gelatin and Its Application as a Wound Healing Therapeutic Agent</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1335,22 +1343,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ardas Daruslam</t>
+          <t>Ahmad Haikal Kadir</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>National Nutrition Agency</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Vegetable Waste Eco-Enzyme Technology</t>
+          <t>Fruits Waste Enzyme Technology</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1372,22 +1380,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ilham Reswara</t>
+          <t>Muhammad Ardas Daruslam</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>National Nutrition Agency</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Characteristics of Horse Skin Gelatin and Its Application in Edible Films</t>
+          <t>Vegetable Waste Eco-Enzyme Technology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1409,12 +1417,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Abdul Khaer</t>
+          <t>Muhammad Ilham Reswara</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1424,7 +1432,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Enzymatic and Bacterial Hydrolysis on the Quality of Horse Skin Gelatin</t>
+          <t>Characteristics of Horse Skin Gelatin and Its Application in Edible Films</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1446,12 +1454,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Andi Sartika Eka Putri</t>
+          <t>Abdul Khaer</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1461,7 +1469,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Acid and Alkaline Hydrolysis on the Quality of Horse Skin Gelatin</t>
+          <t>The Effect of Enzymatic and Bacterial Hydrolysis on the Quality of Horse Skin Gelatin</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1483,12 +1491,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Nur Azizah Taufiq</t>
+          <t>Andi Sartika Eka Putri</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Using Teak Wood Flour (Tectona grandis) as a Tanning Material on Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
+          <t>The Effect of Acid and Alkaline Hydrolysis on the Quality of Horse Skin Gelatin</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1520,12 +1528,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Gabriella Romaito Br Manalu</t>
+          <t>Nur Azizah Taufiq</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1535,7 +1543,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Water Hyacinth (Eichhornia crassipes) Extract as a Tanning Agent on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
+          <t>The Effect of Using Teak Wood Flour (Tectona grandis) as a Tanning Material on Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1557,12 +1565,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Sarjita Sarunan</t>
+          <t>Gabriella Romaito Br Manalu</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1572,7 +1580,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Guava Leaf (Psidium guajava) Extract on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
+          <t>The Effect of Water Hyacinth (Eichhornia crassipes) Extract as a Tanning Agent on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1594,12 +1602,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Altifany Imanda Putri Hakim</t>
+          <t>Sarjita Sarunan</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1609,7 +1617,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Mangosteen Peel (Garcinia mangostana) as a Tanning Agent on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
+          <t>The Effect of Guava Leaf (Psidium guajava) Extract on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1631,12 +1639,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Andi Muh Nurcholish Pasha</t>
+          <t>Altifany Imanda Putri Hakim</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1646,7 +1654,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Sappan Wood (Caesalpinia sappan) Powder as a Tanning Agent on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
+          <t>The Effect of Mangosteen Peel (Garcinia mangostana) as a Tanning Agent on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1666,10 +1674,26 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Andi Muh Nurcholish Pasha</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>The Effect of Sappan Wood (Caesalpinia sappan) Powder as a Tanning Agent on the Antibacterial Activity of Vegetable-Tanned Goat Leather</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -1677,7 +1701,11 @@
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1866,15 +1894,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
